--- a/AAAGameData/DataTables/ItemGroupTable.xlsx
+++ b/AAAGameData/DataTables/ItemGroupTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
   <si>
     <t>#</t>
   </si>
@@ -93,6 +93,24 @@
   </si>
   <si>
     <t>5,6</t>
+  </si>
+  <si>
+    <t>稀有卡牌解锁物</t>
+  </si>
+  <si>
+    <t>100,103,106,107,108,112,120,122,123</t>
+  </si>
+  <si>
+    <t>史诗卡牌解锁物</t>
+  </si>
+  <si>
+    <t>101,102,104,105,110,113,114,115,116,117,118,119,121</t>
+  </si>
+  <si>
+    <t>传说卡牌解锁物</t>
+  </si>
+  <si>
+    <t>109,111</t>
   </si>
 </sst>
 </file>
@@ -713,20 +731,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1074,194 +1085,177 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="8" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="28" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="55.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="4"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="2"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="2" t="s">
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="2" t="s">
+      <c r="C3" s="1"/>
+      <c r="D3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:5">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1">
         <v>1</v>
       </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="2" t="s">
+      <c r="C5" s="1"/>
+      <c r="D5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:5">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1">
         <v>2</v>
       </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="2" t="s">
+      <c r="C6" s="1"/>
+      <c r="D6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:5">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1">
         <v>3</v>
       </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="2" t="s">
+      <c r="C7" s="1"/>
+      <c r="D7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:5">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1">
         <v>4</v>
       </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="2" t="s">
+      <c r="C8" s="1"/>
+      <c r="D8" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
-      <c r="B9">
+    <row r="9" ht="15" customHeight="1" spans="1:5">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1">
         <v>5</v>
       </c>
-      <c r="C9" s="5"/>
-      <c r="D9" t="s">
+      <c r="C9" s="1"/>
+      <c r="D9" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
-      <c r="C10" s="5"/>
+    <row r="10" ht="15" customHeight="1" spans="1:5">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1">
+        <v>6</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="11" spans="1:5">
-      <c r="C11" s="5"/>
+    <row r="11" ht="15" customHeight="1" spans="1:5">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1">
+        <v>7</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="12" spans="1:5">
-      <c r="C12" s="5"/>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="C13" s="5"/>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="C14" s="5"/>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="C15" s="5"/>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="C16" s="5"/>
-    </row>
-    <row r="17" spans="3:3">
-      <c r="C17" s="5"/>
-    </row>
-    <row r="18" spans="3:3">
-      <c r="C18" s="5"/>
-    </row>
-    <row r="19" spans="3:3">
-      <c r="C19" s="5"/>
-    </row>
-    <row r="20" spans="3:3">
-      <c r="C20" s="5"/>
-    </row>
-    <row r="21" spans="3:3">
-      <c r="C21" s="5"/>
-    </row>
-    <row r="22" spans="3:3">
-      <c r="C22" s="5"/>
-    </row>
-    <row r="23" spans="3:3">
-      <c r="C23" s="5"/>
-    </row>
-    <row r="24" spans="3:3">
-      <c r="C24" s="5"/>
-    </row>
-    <row r="25" spans="3:3">
-      <c r="C25" s="5"/>
-    </row>
-    <row r="26" spans="3:3">
-      <c r="C26" s="5"/>
-    </row>
-    <row r="27" spans="3:3">
-      <c r="C27" s="5"/>
-    </row>
-    <row r="28" spans="3:3">
-      <c r="C28" s="5"/>
+    <row r="12" ht="15" customHeight="1" spans="1:5">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1">
+        <v>8</v>
+      </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/AAAGameData/DataTables/ItemGroupTable.xlsx
+++ b/AAAGameData/DataTables/ItemGroupTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="30">
   <si>
     <t>#</t>
   </si>
@@ -111,6 +111,12 @@
   </si>
   <si>
     <t>109,111</t>
+  </si>
+  <si>
+    <t>神秘钥匙</t>
+  </si>
+  <si>
+    <t>5</t>
   </si>
 </sst>
 </file>
@@ -123,14 +129,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -586,148 +585,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1085,7 +1084,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1257,6 +1256,17 @@
         <v>27</v>
       </c>
     </row>
+    <row r="13" spans="1:5">
+      <c r="B13">
+        <v>9</v>
+      </c>
+      <c r="D13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/AAAGameData/DataTables/ItemGroupTable.xlsx
+++ b/AAAGameData/DataTables/ItemGroupTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11925"/>
+    <workbookView windowWidth="29868" windowHeight="14855"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="59">
   <si>
     <t>#</t>
   </si>
@@ -117,6 +117,93 @@
   </si>
   <si>
     <t>5</t>
+  </si>
+  <si>
+    <t>品质3装备</t>
+  </si>
+  <si>
+    <t>品质4装备</t>
+  </si>
+  <si>
+    <t>品质5宝物</t>
+  </si>
+  <si>
+    <t>所有装备</t>
+  </si>
+  <si>
+    <t>10,11,12,19,20,21,22,23,24</t>
+  </si>
+  <si>
+    <t>所有宝物</t>
+  </si>
+  <si>
+    <t>所有消耗品</t>
+  </si>
+  <si>
+    <t>所有卡牌解锁物</t>
+  </si>
+  <si>
+    <t>100,101,102,103,104,105,106,107,108,109,110,111,112,113,114,115,116,117,118,119,120,121,122,123</t>
+  </si>
+  <si>
+    <t>品质1物品</t>
+  </si>
+  <si>
+    <t>2,3,999</t>
+  </si>
+  <si>
+    <t>品质2物品</t>
+  </si>
+  <si>
+    <t>1,100,103,106,107,108,112,120,122,123</t>
+  </si>
+  <si>
+    <t>品质3物品</t>
+  </si>
+  <si>
+    <t>4,5,12,20,22,23,101,102,104,105,110,113,114,115,116,117,118,119,121,99999</t>
+  </si>
+  <si>
+    <t>品质4物品</t>
+  </si>
+  <si>
+    <t>6,10,11,19,21,24,109,111,9999</t>
+  </si>
+  <si>
+    <t>品质5物品</t>
+  </si>
+  <si>
+    <t>货币类</t>
+  </si>
+  <si>
+    <t>999,9999,99999</t>
+  </si>
+  <si>
+    <t>任务道具</t>
+  </si>
+  <si>
+    <t>日系神器</t>
+  </si>
+  <si>
+    <t>7,8,9</t>
+  </si>
+  <si>
+    <t>中式神器</t>
+  </si>
+  <si>
+    <t>13,14,15</t>
+  </si>
+  <si>
+    <t>炎魔套装</t>
+  </si>
+  <si>
+    <t>16,17,18</t>
+  </si>
+  <si>
+    <t>稀有品质及以上</t>
+  </si>
+  <si>
+    <t>4,5,12,20,22,23,101,102,104,105,110,113,114,115,116,117,118,119,121,99999,6,10,11,19,21,24,109,111,9999,7,8,9,13,14,15,16,17,18</t>
   </si>
 </sst>
 </file>
@@ -129,7 +216,14 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -585,148 +679,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1084,14 +1178,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="55.625" customWidth="1"/>
+    <col min="5" max="5" width="50" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1256,15 +1350,251 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
-      <c r="B13">
+    <row r="13" ht="15" customHeight="1" spans="1:5">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1">
         <v>9</v>
       </c>
-      <c r="D13" t="s">
+      <c r="C13" s="1"/>
+      <c r="D13" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>29</v>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1" spans="1:5">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1">
+        <v>10</v>
+      </c>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1" spans="1:5">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1">
+        <v>11</v>
+      </c>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1" spans="1:5">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1">
+        <v>15</v>
+      </c>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1" spans="1:5">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1">
+        <v>16</v>
+      </c>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1" spans="1:5">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1">
+        <v>17</v>
+      </c>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1" spans="1:5">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1">
+        <v>18</v>
+      </c>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1" spans="1:5">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1">
+        <v>19</v>
+      </c>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1" spans="1:5">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1">
+        <v>20</v>
+      </c>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1" spans="1:5">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1">
+        <v>21</v>
+      </c>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1" spans="1:5">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1">
+        <v>22</v>
+      </c>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1" spans="1:5">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1">
+        <v>23</v>
+      </c>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1" spans="1:5">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1">
+        <v>24</v>
+      </c>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1" spans="1:5">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1">
+        <v>25</v>
+      </c>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1" spans="1:5">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1">
+        <v>26</v>
+      </c>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1" spans="1:5">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1">
+        <v>27</v>
+      </c>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1" spans="1:5">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1">
+        <v>28</v>
+      </c>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1" spans="1:5">
+      <c r="A30" s="1"/>
+      <c r="B30" s="1">
+        <v>29</v>
+      </c>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1" spans="1:5">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1">
+        <v>30</v>
+      </c>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
